--- a/class 6 addmission doc/Copy of Class 6 Admission Info.xlsx
+++ b/class 6 addmission doc/Copy of Class 6 Admission Info.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atosh\OneDrive\Desktop\Study-Game\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atosh\OneDrive\Desktop\Study-Game\class 6 addmission doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9153F390-2AD0-4E94-8E73-3D895C612E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45A2C1B-D8DE-4AEB-96AD-F705CF0BDBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="joya" sheetId="11" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="90">
   <si>
     <t>নাম</t>
   </si>
@@ -134,9 +134,6 @@
     <t>KANIAL KHTA PONDIT PARA</t>
   </si>
   <si>
-    <t>sumaiya Islam</t>
-  </si>
-  <si>
     <t>02-09-2012</t>
   </si>
   <si>
@@ -206,9 +203,6 @@
     <t>5974626771</t>
   </si>
   <si>
-    <t>KANIAL KHATA boiragi PARA</t>
-  </si>
-  <si>
     <t>DOKKHIN KANIAL KHaTA MASTAR PARA</t>
   </si>
   <si>
@@ -230,9 +224,6 @@
     <t>5524458683</t>
   </si>
   <si>
-    <t>vagirathi rany</t>
-  </si>
-  <si>
     <t>3294062249</t>
   </si>
   <si>
@@ -254,9 +245,6 @@
     <t>19947316431000240</t>
   </si>
   <si>
-    <t>mst. Mahmuda Khatun</t>
-  </si>
-  <si>
     <t>19947316431000306</t>
   </si>
   <si>
@@ -275,24 +263,12 @@
     <t>01346468836</t>
   </si>
   <si>
-    <t xml:space="preserve">Nur mohammad </t>
-  </si>
-  <si>
     <t>6448364239</t>
   </si>
   <si>
-    <t>mrs. Nasima Begum</t>
-  </si>
-  <si>
     <t>4640446003</t>
   </si>
   <si>
-    <t>KANIAL KHATA munsipara</t>
-  </si>
-  <si>
-    <t>KANIAL KHATA</t>
-  </si>
-  <si>
     <t>jaya rani</t>
   </si>
   <si>
@@ -305,16 +281,43 @@
     <t>01326026347</t>
   </si>
   <si>
-    <t>sree narayan roy</t>
-  </si>
-  <si>
     <t>7316431492642</t>
   </si>
   <si>
-    <t>sreemoty trisna rani</t>
-  </si>
-  <si>
     <t>9155936843</t>
+  </si>
+  <si>
+    <t>Sree Narayan Roy</t>
+  </si>
+  <si>
+    <t>Sreemoty Trisna Rani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nur Mohammad </t>
+  </si>
+  <si>
+    <t>Mrs. Nasima Begum</t>
+  </si>
+  <si>
+    <t>KANIAL KHATA Munsipara</t>
+  </si>
+  <si>
+    <t>Mst. Mahmuda Khatun</t>
+  </si>
+  <si>
+    <t>Kanialkhata</t>
+  </si>
+  <si>
+    <t>Kanial Khata Boiragi Para</t>
+  </si>
+  <si>
+    <t>Vagirathi Rany</t>
+  </si>
+  <si>
+    <t>Sumaiya Islam</t>
+  </si>
+  <si>
+    <t>DOKKHIN KANIAL KHATA MASTAR PARA</t>
   </si>
 </sst>
 </file>
@@ -674,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -682,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -690,7 +693,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -698,7 +701,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -706,7 +709,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -714,7 +717,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -722,7 +725,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -730,7 +733,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -738,7 +741,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -780,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -788,7 +791,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -796,7 +799,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -804,7 +807,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -812,7 +815,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -820,7 +823,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -828,7 +831,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -836,7 +839,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -844,7 +847,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -877,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -885,7 +888,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -893,7 +896,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -901,7 +904,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -909,7 +912,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -917,7 +920,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -925,7 +928,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -933,7 +936,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -941,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -974,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -982,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -990,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -998,7 +1001,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1006,7 +1009,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1014,7 +1017,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1022,7 +1025,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1030,7 +1033,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1038,7 +1041,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1071,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1079,7 +1082,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1087,7 +1090,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1095,7 +1098,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1103,7 +1106,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1111,7 +1114,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1119,7 +1122,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1127,7 +1130,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1135,7 +1138,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1168,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1176,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1184,7 +1187,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1192,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1200,7 +1203,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1208,7 +1211,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1216,7 +1219,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1224,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1232,7 +1235,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1265,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1273,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1281,7 +1284,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1289,7 +1292,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1297,7 +1300,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1305,7 +1308,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1313,7 +1316,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1321,7 +1324,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1329,7 +1332,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1523,7 +1526,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
